--- a/Datas/FestivalDataList.xlsx
+++ b/Datas/FestivalDataList.xlsx
@@ -429,6 +429,7 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="37.625" customWidth="1"/>
     <col min="5" max="5" width="13.75" customWidth="1"/>
   </cols>
   <sheetData>
